--- a/rapporten/prijsrapport-NL-2026-05-20.xlsx
+++ b/rapporten/prijsrapport-NL-2026-05-20.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="133">
   <si>
     <t>Product</t>
   </si>
@@ -385,10 +385,10 @@
     <t>8721055493228</t>
   </si>
   <si>
-    <t>Sentio What Happens Under The Mistletoe Stays Under The Mistletoe - Eau de parfum</t>
-  </si>
-  <si>
-    <t>8721055492795</t>
+    <t>Azira - Dream Oasis - Eau de Parfum Unisex</t>
+  </si>
+  <si>
+    <t>8721349102706</t>
   </si>
   <si>
     <t>Dorsh</t>
@@ -410,12 +410,6 @@
   </si>
   <si>
     <t>8719214757229</t>
-  </si>
-  <si>
-    <t>Azira - Dream Oasis - Eau de Parfum Unisex</t>
-  </si>
-  <si>
-    <t>8721349102706</t>
   </si>
 </sst>
 </file>
@@ -807,7 +801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -2310,19 +2304,19 @@
         <v>125</v>
       </c>
       <c r="C58" s="1">
-        <v>7.25</v>
+        <v>14.25</v>
       </c>
       <c r="D58" s="1">
-        <v>7.02</v>
+        <v>14.25</v>
       </c>
       <c r="E58" s="1">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="F58" t="s">
         <v>126</v>
       </c>
       <c r="G58" s="1">
-        <v>7.02</v>
+        <v>14.25</v>
       </c>
       <c r="H58" t="s">
         <v>11</v>
@@ -2339,16 +2333,16 @@
         <v>14.05</v>
       </c>
       <c r="D59" s="1">
-        <v>13.84</v>
+        <v>14.05</v>
       </c>
       <c r="E59" s="1">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="F59" t="s">
         <v>126</v>
       </c>
       <c r="G59" s="1">
-        <v>13.84</v>
+        <v>14.05</v>
       </c>
       <c r="H59" t="s">
         <v>11</v>
@@ -2365,16 +2359,16 @@
         <v>9.79</v>
       </c>
       <c r="D60" s="1">
-        <v>9.61</v>
+        <v>9.79</v>
       </c>
       <c r="E60" s="1">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="F60" t="s">
         <v>126</v>
       </c>
       <c r="G60" s="1">
-        <v>9.61</v>
+        <v>9.79</v>
       </c>
       <c r="H60" t="s">
         <v>11</v>
@@ -2391,44 +2385,18 @@
         <v>9.79</v>
       </c>
       <c r="D61" s="1">
-        <v>9.64</v>
+        <v>9.79</v>
       </c>
       <c r="E61" s="1">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="F61" t="s">
         <v>126</v>
       </c>
       <c r="G61" s="1">
-        <v>9.64</v>
+        <v>9.79</v>
       </c>
       <c r="H61" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>133</v>
-      </c>
-      <c r="B62" t="s">
-        <v>134</v>
-      </c>
-      <c r="C62" s="1">
-        <v>14.25</v>
-      </c>
-      <c r="D62" s="1">
-        <v>14.12</v>
-      </c>
-      <c r="E62" s="1">
-        <v>0.13</v>
-      </c>
-      <c r="F62" t="s">
-        <v>126</v>
-      </c>
-      <c r="G62" s="1">
-        <v>14.12</v>
-      </c>
-      <c r="H62" t="s">
         <v>11</v>
       </c>
     </row>
